--- a/pregenereated_results/s2/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
+++ b/pregenereated_results/s2/ate_iptw_gee_IPTW_GEE_manager_efficacy_index.xlsx
@@ -1388,7 +1388,7 @@
         <v>7220</v>
       </c>
       <c r="B2" t="n">
-        <v>7094.386718944054</v>
+        <v>7094.386718944053</v>
       </c>
       <c r="C2" t="n">
         <v>0.9957648995493169</v>
@@ -1397,13 +1397,13 @@
         <v>0.1325095691671194</v>
       </c>
       <c r="E2" t="n">
-        <v>1.678870188120528</v>
+        <v>1.678870188120527</v>
       </c>
       <c r="F2" t="n">
         <v>1.124267686541995</v>
       </c>
       <c r="G2" t="n">
-        <v>1.67804342107184</v>
+        <v>1.678043421071839</v>
       </c>
     </row>
   </sheetData>
@@ -1467,16 +1467,16 @@
         <v>1.749032162934507</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0997233061900074</v>
+        <v>0.09972330619000462</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553578074382832</v>
+        <v>1.553578074382837</v>
       </c>
       <c r="E2" t="n">
-        <v>1.944486251486182</v>
+        <v>1.944486251486176</v>
       </c>
       <c r="F2" t="n">
-        <v>7.237657289196959e-69</v>
+        <v>7.237657289135669e-69</v>
       </c>
       <c r="G2" t="n">
         <v>0.05</v>
@@ -1489,19 +1489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02962572488141942</v>
+        <v>0.02962572488141944</v>
       </c>
       <c r="C3" t="n">
         <v>0.01822264113750337</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.006089995451285204</v>
+        <v>-0.00608999545128517</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06534144521412404</v>
+        <v>0.06534144521412405</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1039997416774884</v>
+        <v>0.103999741677488</v>
       </c>
       <c r="G3" t="n">
         <v>0.05</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09776307597911857</v>
+        <v>0.09776307597911855</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04954667549874947</v>
+        <v>0.04954667549874944</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0006533764478764831</v>
+        <v>0.0006533764478765247</v>
       </c>
       <c r="E4" t="n">
         <v>0.1948727755103606</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04847835276759659</v>
+        <v>0.04847835276759649</v>
       </c>
       <c r="G4" t="n">
         <v>0.05</v>
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.0128759363155794</v>
+        <v>-0.01287593631557939</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03341847660338247</v>
+        <v>0.03341847660338249</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.07837494687640348</v>
+        <v>-0.07837494687640349</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05262307424524468</v>
+        <v>0.05262307424524471</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7000196553266504</v>
+        <v>0.7000196553266508</v>
       </c>
       <c r="G5" t="n">
         <v>0.05</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04934458162077567</v>
+        <v>0.04934458162077574</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03238690772777993</v>
+        <v>0.03238690772777992</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.01413259109629494</v>
+        <v>-0.01413259109629485</v>
       </c>
       <c r="E6" t="n">
         <v>0.1128217543378463</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1276095198106732</v>
+        <v>0.1276095198106726</v>
       </c>
       <c r="G6" t="n">
         <v>0.05</v>
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01045597826565331</v>
+        <v>0.01045597826565334</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03252310347467072</v>
+        <v>0.0325231034746707</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05328813321017078</v>
+        <v>-0.05328813321017072</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0742000897414774</v>
+        <v>0.07420008974147739</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478361600842374</v>
+        <v>0.7478361600842367</v>
       </c>
       <c r="G7" t="n">
         <v>0.05</v>
@@ -1614,19 +1614,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06434814183682909</v>
+        <v>0.0643481418368291</v>
       </c>
       <c r="C8" t="n">
         <v>0.03290386814872377</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0001422546867241303</v>
+        <v>-0.0001422546867241165</v>
       </c>
       <c r="E8" t="n">
         <v>0.1288385383603823</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05050750165873737</v>
+        <v>0.05050750165873732</v>
       </c>
       <c r="G8" t="n">
         <v>0.05</v>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02877420831517304</v>
+        <v>0.02877420831517306</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03191215009447936</v>
+        <v>0.03191215009447935</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.03377245653924299</v>
+        <v>-0.03377245653924295</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09132087316958906</v>
+        <v>0.09132087316958908</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3672325279422073</v>
+        <v>0.3672325279422067</v>
       </c>
       <c r="G9" t="n">
         <v>0.05</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.00101898420932277</v>
+        <v>-0.001018984209322789</v>
       </c>
       <c r="C10" t="n">
-        <v>0.05063846000222128</v>
+        <v>0.05063846000222123</v>
       </c>
       <c r="D10" t="n">
         <v>-0.1002685420462485</v>
       </c>
       <c r="E10" t="n">
-        <v>0.09823057362760301</v>
+        <v>0.09823057362760287</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9839454655173241</v>
+        <v>0.9839454655173238</v>
       </c>
       <c r="G10" t="n">
         <v>0.05</v>
@@ -1689,19 +1689,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.01931633161945881</v>
+        <v>0.01931633161945882</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05194329107217195</v>
+        <v>0.05194329107217199</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.08249064812047914</v>
+        <v>-0.08249064812047921</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1211233113593968</v>
+        <v>0.1211233113593969</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7099870626555924</v>
+        <v>0.7099870626555926</v>
       </c>
       <c r="G11" t="n">
         <v>0.05</v>
@@ -1717,16 +1717,16 @@
         <v>0.0677289801249665</v>
       </c>
       <c r="C12" t="n">
-        <v>0.05163557818882266</v>
+        <v>0.0516355781888226</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.03347489344602786</v>
+        <v>-0.03347489344602775</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1689328536959609</v>
+        <v>0.1689328536959608</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1896305795997606</v>
+        <v>0.18963057959976</v>
       </c>
       <c r="G12" t="n">
         <v>0.05</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03988129614662063</v>
+        <v>0.03988129614662066</v>
       </c>
       <c r="C13" t="n">
-        <v>0.05171813694708186</v>
+        <v>0.0517181369470819</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.06148438961717011</v>
+        <v>-0.06148438961717016</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1412469819104114</v>
+        <v>0.1412469819104115</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4406311499162626</v>
+        <v>0.4406311499162627</v>
       </c>
       <c r="G13" t="n">
         <v>0.05</v>
@@ -1764,19 +1764,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01333034569364371</v>
+        <v>0.01333034569364382</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05322085593893354</v>
+        <v>0.0532208559389335</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.09098061517306066</v>
+        <v>-0.0909806151730605</v>
       </c>
       <c r="E14" t="n">
         <v>0.1176413065603481</v>
       </c>
       <c r="F14" t="n">
-        <v>0.802222188907029</v>
+        <v>0.8022221889070273</v>
       </c>
       <c r="G14" t="n">
         <v>0.05</v>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05372608150388216</v>
+        <v>0.05372608150388213</v>
       </c>
       <c r="C15" t="n">
-        <v>0.05226717408728829</v>
+        <v>0.05226717408728838</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.04871569728088807</v>
+        <v>-0.04871569728088826</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1561678602886524</v>
+        <v>0.1561678602886525</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3039909897906226</v>
+        <v>0.3039909897906238</v>
       </c>
       <c r="G15" t="n">
         <v>0.05</v>
@@ -1814,19 +1814,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.04075528353732605</v>
+        <v>0.04075528353732606</v>
       </c>
       <c r="C16" t="n">
-        <v>0.05309570953627988</v>
+        <v>0.05309570953627994</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.06331039488738241</v>
+        <v>-0.06331039488738252</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1448209619620345</v>
+        <v>0.1448209619620346</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4427358660730101</v>
+        <v>0.4427358660730105</v>
       </c>
       <c r="G16" t="n">
         <v>0.05</v>
@@ -1842,16 +1842,16 @@
         <v>0.01088254976687354</v>
       </c>
       <c r="C17" t="n">
-        <v>0.05158432471739408</v>
+        <v>0.05158432471739419</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.09022086884603817</v>
+        <v>-0.09022086884603836</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1119859683797853</v>
+        <v>0.1119859683797854</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8329136341204477</v>
+        <v>0.8329136341204481</v>
       </c>
       <c r="G17" t="n">
         <v>0.05</v>
@@ -1864,19 +1864,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0286319469098267</v>
+        <v>0.02863194690982666</v>
       </c>
       <c r="C18" t="n">
-        <v>0.04992876705012336</v>
+        <v>0.04992876705012337</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.06922663830090525</v>
+        <v>-0.06922663830090531</v>
       </c>
       <c r="E18" t="n">
         <v>0.1264905321205586</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5663360387177493</v>
+        <v>0.5663360387177497</v>
       </c>
       <c r="G18" t="n">
         <v>0.05</v>
@@ -1889,19 +1889,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.009518215481816597</v>
+        <v>0.009518215481816599</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05189167694291168</v>
+        <v>0.0518916769429116</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.09218760242367784</v>
+        <v>-0.09218760242367767</v>
       </c>
       <c r="E19" t="n">
-        <v>0.111224033387311</v>
+        <v>0.1112240333873109</v>
       </c>
       <c r="F19" t="n">
-        <v>0.854464793714935</v>
+        <v>0.8544647937149347</v>
       </c>
       <c r="G19" t="n">
         <v>0.05</v>
@@ -1914,19 +1914,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.01322088667279</v>
+        <v>-0.01322088667279006</v>
       </c>
       <c r="C20" t="n">
-        <v>0.04979291726953827</v>
+        <v>0.04979291726953838</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1108132112062675</v>
+        <v>-0.1108132112062678</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0843714378606875</v>
+        <v>0.08437143786068765</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7906108960257916</v>
+        <v>0.790610896025791</v>
       </c>
       <c r="G20" t="n">
         <v>0.05</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.004335437062310128</v>
+        <v>0.004335437062310145</v>
       </c>
       <c r="C21" t="n">
-        <v>0.05125049584123835</v>
+        <v>0.05125049584123829</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.09611368897633686</v>
+        <v>-0.09611368897633674</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1047845631009571</v>
+        <v>0.104784563100957</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9325849043145348</v>
+        <v>0.9325849043145344</v>
       </c>
       <c r="G21" t="n">
         <v>0.05</v>
@@ -1964,19 +1964,19 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.01158397950368169</v>
+        <v>0.01158397950368181</v>
       </c>
       <c r="C22" t="n">
-        <v>0.05351623953049025</v>
+        <v>0.05351623953049019</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.09330592256409793</v>
+        <v>-0.09330592256409768</v>
       </c>
       <c r="E22" t="n">
         <v>0.1164738815714613</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8286313234472755</v>
+        <v>0.8286313234472735</v>
       </c>
       <c r="G22" t="n">
         <v>0.05</v>
@@ -1989,19 +1989,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.04490126550683204</v>
+        <v>0.04490126550683207</v>
       </c>
       <c r="C23" t="n">
-        <v>0.05073590126058453</v>
+        <v>0.05073590126058455</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.05453927368709396</v>
+        <v>-0.05453927368709397</v>
       </c>
       <c r="E23" t="n">
-        <v>0.144341804700758</v>
+        <v>0.1443418047007581</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3761567069305498</v>
+        <v>0.3761567069305497</v>
       </c>
       <c r="G23" t="n">
         <v>0.05</v>
@@ -2014,19 +2014,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.09277287691209153</v>
+        <v>0.09277287691209132</v>
       </c>
       <c r="C24" t="n">
-        <v>0.04198074945144141</v>
+        <v>0.0419807494514414</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01049211994326674</v>
+        <v>0.01049211994326654</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1750536338809163</v>
+        <v>0.1750536338809161</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02711273375311711</v>
+        <v>0.02711273375311746</v>
       </c>
       <c r="G24" t="n">
         <v>0.05</v>
@@ -2039,16 +2039,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0360786356075037</v>
+        <v>0.03607863560750364</v>
       </c>
       <c r="C25" t="n">
-        <v>0.02485846017140067</v>
+        <v>0.02485846017140063</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.01264305103956499</v>
+        <v>-0.01264305103956498</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0848003222545724</v>
+        <v>0.08480032225457225</v>
       </c>
       <c r="F25" t="n">
         <v>0.1466789605900473</v>
@@ -2064,19 +2064,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.01448398768324711</v>
+        <v>0.0144839876832471</v>
       </c>
       <c r="C26" t="n">
-        <v>0.02811551845289983</v>
+        <v>0.02811551845289984</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.04062141589110786</v>
+        <v>-0.04062141589110788</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06958939125760208</v>
+        <v>0.06958939125760209</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6064412877410574</v>
+        <v>0.6064412877410577</v>
       </c>
       <c r="G26" t="n">
         <v>0.05</v>
@@ -2089,19 +2089,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.03309843316687123</v>
+        <v>-0.0330984331668712</v>
       </c>
       <c r="C27" t="n">
-        <v>0.02920935542237533</v>
+        <v>0.02920935542237534</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.09034771780635661</v>
+        <v>-0.09034771780635659</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02415085147261416</v>
+        <v>0.02415085147261419</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2571533936244728</v>
+        <v>0.2571533936244732</v>
       </c>
       <c r="G27" t="n">
         <v>0.05</v>
@@ -2114,19 +2114,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.01378326527887544</v>
+        <v>-0.01378326527887543</v>
       </c>
       <c r="C28" t="n">
-        <v>0.02964373700932217</v>
+        <v>0.0296437370093222</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.07188392218432399</v>
+        <v>-0.07188392218432405</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0443173916265731</v>
+        <v>0.04431739162657319</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6419573641976883</v>
+        <v>0.641957364197689</v>
       </c>
       <c r="G28" t="n">
         <v>0.05</v>
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.02693520877969164</v>
+        <v>-0.02693520877969161</v>
       </c>
       <c r="C29" t="n">
         <v>0.02936902969487703</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.08449744924253799</v>
+        <v>-0.08449744924253796</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03062703168315472</v>
+        <v>0.03062703168315475</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3590746904262956</v>
+        <v>0.359074690426296</v>
       </c>
       <c r="G29" t="n">
         <v>0.05</v>
@@ -2164,19 +2164,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3982233096578141</v>
+        <v>0.3982233096578142</v>
       </c>
       <c r="C30" t="n">
-        <v>0.03926983810596111</v>
+        <v>0.03926983810596112</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3212558412914117</v>
+        <v>0.3212558412914118</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4751907780242164</v>
+        <v>0.4751907780242166</v>
       </c>
       <c r="F30" t="n">
-        <v>3.645104327879786e-24</v>
+        <v>3.645104327879733e-24</v>
       </c>
       <c r="G30" t="n">
         <v>0.05</v>
@@ -2185,23 +2185,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.002085975822998771</v>
+        <v>1.638035829451045</v>
       </c>
       <c r="C31" t="n">
-        <v>0.001402357375237836</v>
+        <v>0.04812529240022895</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.004834545771919052</v>
+        <v>1.543711989601137</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0006625941259215105</v>
+        <v>1.732359669300953</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1368885945885609</v>
+        <v>6.341968535469546e-254</v>
       </c>
       <c r="G31" t="n">
         <v>0.05</v>
@@ -2214,19 +2214,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.001517501047856209</v>
+        <v>-0.001517501047856198</v>
       </c>
       <c r="C32" t="n">
-        <v>0.00159977479550116</v>
+        <v>0.00159977479550119</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.004653002030413412</v>
+        <v>-0.004653002030413462</v>
       </c>
       <c r="E32" t="n">
-        <v>0.001617999934700994</v>
+        <v>0.001617999934701065</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3428385058225838</v>
+        <v>0.3428385058225965</v>
       </c>
       <c r="G32" t="n">
         <v>0.05</v>
@@ -2235,23 +2235,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>baseline_manager_efficacy</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4975842499220143</v>
+        <v>-0.002085975822998772</v>
       </c>
       <c r="C33" t="n">
-        <v>0.01226979046800349</v>
+        <v>0.001402357375237834</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4735359025068746</v>
+        <v>-0.004834545771919049</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5216325973371539</v>
+        <v>0.0006625941259215049</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>0.1368885945885599</v>
       </c>
       <c r="G33" t="n">
         <v>0.05</v>
@@ -2264,19 +2264,19 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.003190404661875361</v>
+        <v>-0.003190404661875355</v>
       </c>
       <c r="C34" t="n">
-        <v>0.004191906749099856</v>
+        <v>0.004191906749099821</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.01140639091666146</v>
+        <v>-0.01140639091666138</v>
       </c>
       <c r="E34" t="n">
-        <v>0.005025581592910739</v>
+        <v>0.005025581592910674</v>
       </c>
       <c r="F34" t="n">
-        <v>0.4466052571656757</v>
+        <v>0.4466052571656727</v>
       </c>
       <c r="G34" t="n">
         <v>0.05</v>
@@ -2285,23 +2285,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>tot_span_of_control</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.638035829451045</v>
+        <v>0.001072258730903538</v>
       </c>
       <c r="C35" t="n">
-        <v>0.04812529240022996</v>
+        <v>0.001289206013563251</v>
       </c>
       <c r="D35" t="n">
-        <v>1.543711989601135</v>
+        <v>-0.00145453862433289</v>
       </c>
       <c r="E35" t="n">
-        <v>1.732359669300955</v>
+        <v>0.003599056086139966</v>
       </c>
       <c r="F35" t="n">
-        <v>6.341968535623971e-254</v>
+        <v>0.4055668752339284</v>
       </c>
       <c r="G35" t="n">
         <v>0.05</v>
@@ -2310,23 +2310,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tot_span_of_control</t>
+          <t>baseline_manager_efficacy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.001072258730903541</v>
+        <v>0.4975842499220143</v>
       </c>
       <c r="C36" t="n">
-        <v>0.001289206013563249</v>
+        <v>0.01226979046800327</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.001454538624332883</v>
+        <v>0.473535902506875</v>
       </c>
       <c r="E36" t="n">
-        <v>0.003599056086139966</v>
+        <v>0.5216325973371535</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4055668752339265</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0.05</v>
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.680600179802938</v>
+        <v>-2.680600179802939</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4771933030981325</v>
+        <v>0.4771933030981503</v>
       </c>
       <c r="D2" t="n">
-        <v>1.938181768271168e-08</v>
+        <v>1.938181768273511e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2394,7 +2394,7 @@
         <v>-0.02542074333516161</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1002143663033997</v>
+        <v>0.1002143663033998</v>
       </c>
       <c r="D3" t="n">
         <v>0.79975540801217</v>
@@ -2410,10 +2410,10 @@
         <v>0.2244463748843409</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2335027157442914</v>
+        <v>0.2335027157442915</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3364439424069159</v>
+        <v>0.3364439424069162</v>
       </c>
     </row>
     <row r="5">
@@ -2426,10 +2426,10 @@
         <v>0.8155080917228588</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1734026513921177</v>
+        <v>0.173402651392118</v>
       </c>
       <c r="D5" t="n">
-        <v>2.563995828054277e-06</v>
+        <v>2.563995828054386e-06</v>
       </c>
     </row>
     <row r="6">
@@ -2439,13 +2439,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03527526670387295</v>
+        <v>0.03527526670387308</v>
       </c>
       <c r="C6" t="n">
-        <v>0.191688294691954</v>
+        <v>0.1916882946919544</v>
       </c>
       <c r="D6" t="n">
-        <v>0.853994545471355</v>
+        <v>0.8539945454713548</v>
       </c>
     </row>
     <row r="7">
@@ -2458,10 +2458,10 @@
         <v>0.2773648159307716</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1901447102133382</v>
+        <v>0.1901447102133385</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1446466431125516</v>
+        <v>0.1446466431125523</v>
       </c>
     </row>
     <row r="8">
@@ -2474,10 +2474,10 @@
         <v>0.1036811851537241</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1952515666982443</v>
+        <v>0.1952515666982444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5954095400432464</v>
+        <v>0.5954095400432469</v>
       </c>
     </row>
     <row r="9">
@@ -2490,10 +2490,10 @@
         <v>0.8738774480300985</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1695280942409136</v>
+        <v>0.1695280942409139</v>
       </c>
       <c r="D9" t="n">
-        <v>2.539495077342701e-07</v>
+        <v>2.539495077342821e-07</v>
       </c>
     </row>
     <row r="10">
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.04456520772617086</v>
+        <v>-0.0445652077261707</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2604021031716313</v>
+        <v>0.260402103171632</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8641137091517834</v>
+        <v>0.8641137091517843</v>
       </c>
     </row>
     <row r="11">
@@ -2519,13 +2519,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2737623724798149</v>
+        <v>-0.2737623724798146</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2787881385465057</v>
+        <v>0.2787881385465067</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3261132423877617</v>
+        <v>0.326113242387764</v>
       </c>
     </row>
     <row r="12">
@@ -2535,10 +2535,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08100487957118127</v>
+        <v>0.08100487957118148</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2596429772097166</v>
+        <v>0.2596429772097172</v>
       </c>
       <c r="D12" t="n">
         <v>0.7550514391424692</v>
@@ -2551,13 +2551,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03917827337461736</v>
+        <v>0.03917827337461754</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2572958805743769</v>
+        <v>0.2572958805743774</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8789745077123745</v>
+        <v>0.8789745077123743</v>
       </c>
     </row>
     <row r="14">
@@ -2567,13 +2567,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05296103812307947</v>
+        <v>-0.05296103812307935</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2610089865588713</v>
+        <v>0.2610089865588724</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8392062624375523</v>
+        <v>0.8392062624375534</v>
       </c>
     </row>
     <row r="15">
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1181322726534159</v>
+        <v>0.1181322726534161</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2572294350577177</v>
+        <v>0.2572294350577187</v>
       </c>
       <c r="D15" t="n">
-        <v>0.646055612898408</v>
+        <v>0.6460556128984086</v>
       </c>
     </row>
     <row r="16">
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.004000986240379581</v>
+        <v>-0.004000986240379481</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2383903410311186</v>
+        <v>0.2383903410311192</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9866094604655129</v>
+        <v>0.9866094604655132</v>
       </c>
     </row>
     <row r="17">
@@ -2615,13 +2615,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1057185310395304</v>
+        <v>0.1057185310395306</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2543340222421748</v>
+        <v>0.2543340222421759</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6776529122567303</v>
+        <v>0.677652912256731</v>
       </c>
     </row>
     <row r="18">
@@ -2631,13 +2631,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1377694895733256</v>
+        <v>-0.1377694895733254</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2636874203313626</v>
+        <v>0.2636874203313636</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6013412201546261</v>
+        <v>0.6013412201546282</v>
       </c>
     </row>
     <row r="19">
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02557154094223238</v>
+        <v>-0.02557154094223237</v>
       </c>
       <c r="C19" t="n">
-        <v>0.252759790153811</v>
+        <v>0.2527597901538116</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9194160355966675</v>
+        <v>0.9194160355966677</v>
       </c>
     </row>
     <row r="20">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.07344622569376427</v>
+        <v>-0.07344622569376411</v>
       </c>
       <c r="C20" t="n">
-        <v>0.267457860954101</v>
+        <v>0.2674578609541021</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7836169672222772</v>
+        <v>0.7836169672222787</v>
       </c>
     </row>
     <row r="21">
@@ -2679,13 +2679,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2063167170305059</v>
+        <v>0.2063167170305062</v>
       </c>
       <c r="C21" t="n">
-        <v>0.244289653245072</v>
+        <v>0.2442896532450728</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3983578134719846</v>
+        <v>0.3983578134719854</v>
       </c>
     </row>
     <row r="22">
@@ -2695,13 +2695,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1704634573362026</v>
+        <v>-0.1704634573362028</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2696748454965904</v>
+        <v>0.269674845496591</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5273167196806361</v>
+        <v>0.5273167196806365</v>
       </c>
     </row>
     <row r="23">
@@ -2711,13 +2711,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5008110927334757</v>
+        <v>-0.5008110927334755</v>
       </c>
       <c r="C23" t="n">
-        <v>0.287067218044571</v>
+        <v>0.2870672180445716</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08105838975171785</v>
+        <v>0.0810583897517186</v>
       </c>
     </row>
     <row r="24">
@@ -2727,13 +2727,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9366864721074267</v>
+        <v>0.9366864721074268</v>
       </c>
       <c r="C24" t="n">
         <v>0.1483430409733375</v>
       </c>
       <c r="D24" t="n">
-        <v>2.713396260923891e-10</v>
+        <v>2.713396260923871e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2746,10 +2746,10 @@
         <v>-0.5776106069409677</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1143619392421807</v>
+        <v>0.1143619392421806</v>
       </c>
       <c r="D25" t="n">
-        <v>4.401383208103943e-07</v>
+        <v>4.401383208103854e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2759,13 +2759,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.237316144844174</v>
+        <v>0.2373161448441742</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1503781926377478</v>
+        <v>0.1503781926377481</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1145360411757813</v>
+        <v>0.1145360411757815</v>
       </c>
     </row>
     <row r="27">
@@ -2775,13 +2775,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04350476117998651</v>
+        <v>-0.04350476117998643</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1611879340386412</v>
+        <v>0.1611879340386415</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7872365295400213</v>
+        <v>0.7872365295400221</v>
       </c>
     </row>
     <row r="28">
@@ -2791,13 +2791,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07514354096975732</v>
+        <v>-0.07514354096975739</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1613683918223567</v>
+        <v>0.1613683918223571</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6414556246120151</v>
+        <v>0.6414556246120158</v>
       </c>
     </row>
     <row r="29">
@@ -2807,29 +2807,29 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09749293462742097</v>
+        <v>0.09749293462742094</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1543265796290165</v>
+        <v>0.1543265796290169</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5275624553510008</v>
+        <v>0.5275624553510021</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tenure_months</t>
+          <t>is_new_manager</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.002418133412192873</v>
+        <v>0.2280638724458788</v>
       </c>
       <c r="C30" t="n">
-        <v>0.007135781003458546</v>
+        <v>0.1146565719927948</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7347043603418277</v>
+        <v>0.04668969945129902</v>
       </c>
     </row>
     <row r="31">
@@ -2839,45 +2839,45 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.005012017390962195</v>
+        <v>-0.005012017390962181</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008304876992455039</v>
+        <v>0.008304876992454899</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5461741835341576</v>
+        <v>0.5461741835341518</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>num_direct_reports</t>
+          <t>tenure_months</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.004129656026475419</v>
+        <v>-0.002418133412192865</v>
       </c>
       <c r="C32" t="n">
-        <v>0.02222260881033174</v>
+        <v>0.007135781003458533</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8525770672961279</v>
+        <v>0.7347043603418282</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>is_new_manager</t>
+          <t>num_direct_reports</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2280638724458785</v>
+        <v>-0.004129656026475429</v>
       </c>
       <c r="C33" t="n">
-        <v>0.1146565719927948</v>
+        <v>0.02222260881033176</v>
       </c>
       <c r="D33" t="n">
-        <v>0.04668969945129923</v>
+        <v>0.8525770672961277</v>
       </c>
     </row>
     <row r="34">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.006335499136474495</v>
+        <v>0.006335499136474494</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006871422968197181</v>
+        <v>0.006871422968197173</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3565249957666435</v>
+        <v>0.3565249957666431</v>
       </c>
     </row>
   </sheetData>
